--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2125,11 +2125,11 @@
         <v>115162361</v>
       </c>
       <c r="B14" t="n">
-        <v>57215</v>
+        <v>57306</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2227,11 +2227,11 @@
         <v>115162360</v>
       </c>
       <c r="B15" t="n">
-        <v>57206</v>
+        <v>57297</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2329,11 +2329,11 @@
         <v>115369280</v>
       </c>
       <c r="B16" t="n">
-        <v>57271</v>
+        <v>57362</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2125,7 +2125,7 @@
         <v>115162361</v>
       </c>
       <c r="B14" t="n">
-        <v>57306</v>
+        <v>57307</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>115162360</v>
       </c>
       <c r="B15" t="n">
-        <v>57297</v>
+        <v>57298</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>115369280</v>
       </c>
       <c r="B16" t="n">
-        <v>57362</v>
+        <v>57363</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2125,7 +2125,7 @@
         <v>115162361</v>
       </c>
       <c r="B14" t="n">
-        <v>57307</v>
+        <v>57315</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>115162360</v>
       </c>
       <c r="B15" t="n">
-        <v>57298</v>
+        <v>57306</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>115369280</v>
       </c>
       <c r="B16" t="n">
-        <v>57363</v>
+        <v>57371</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1993,65 +1993,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113442932</v>
+        <v>115162361</v>
       </c>
       <c r="B13" t="n">
-        <v>106365</v>
+        <v>57315</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219955</v>
+        <v>102621</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>395589</v>
+        <v>395508</v>
       </c>
       <c r="R13" t="n">
-        <v>6370646</v>
+        <v>6370459</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2073,24 +2061,14 @@
           <t>Tranemo</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>OV-Tra-0347-biogeo</t>
-        </is>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>inga blommande</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2099,33 +2077,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Enar Sahlin</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mats Hannevad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115162361</v>
+        <v>115162360</v>
       </c>
       <c r="B14" t="n">
-        <v>57315</v>
+        <v>57306</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2138,16 +2111,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102621</v>
+        <v>102622</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2162,13 +2135,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>395508</v>
+        <v>395586</v>
       </c>
       <c r="R14" t="n">
-        <v>6370459</v>
+        <v>6370534</v>
       </c>
       <c r="S14" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2192,12 +2165,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2224,10 +2197,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115162360</v>
+        <v>115369280</v>
       </c>
       <c r="B15" t="n">
-        <v>57306</v>
+        <v>57371</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2236,20 +2209,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102622</v>
+        <v>100048</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2258,6 +2231,11 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mjällbo, Vg</t>
@@ -2294,12 +2272,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2323,113 +2301,6 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>115369280</v>
-      </c>
-      <c r="B16" t="n">
-        <v>57371</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100048</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Dryobates minor</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Mjällbo, Vg</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>395586</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6370534</v>
-      </c>
-      <c r="S16" t="n">
-        <v>12</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Tranemo</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Tranemo</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Thomas Tranefors</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Thomas Tranefors</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2406,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124227773</v>
+        <v>124227864</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>56942</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,20 +2418,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100091</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2440,6 +2440,11 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>mjällbo, Vg</t>
@@ -2479,9 +2484,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>00:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124227160</v>
+        <v>124227773</v>
       </c>
       <c r="B18" t="n">
-        <v>57532</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2520,25 +2535,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2610,10 +2625,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124226790</v>
+        <v>124227087</v>
       </c>
       <c r="B19" t="n">
-        <v>57948</v>
+        <v>57664</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2626,27 +2641,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102999</v>
+        <v>103020</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>mjällbo, mjällbo, Vg</t>
+          <t>mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -2712,10 +2727,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124227864</v>
+        <v>124226790</v>
       </c>
       <c r="B20" t="n">
-        <v>56942</v>
+        <v>57948</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,36 +2739,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100091</v>
+        <v>102999</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>mjällbo, mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -2790,19 +2800,9 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:35</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124227437</v>
+        <v>124227160</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>57532</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124227087</v>
+        <v>124227437</v>
       </c>
       <c r="B23" t="n">
-        <v>57664</v>
+        <v>57883</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3045,20 +3045,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2304,10 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124226880</v>
+        <v>124227087</v>
       </c>
       <c r="B16" t="n">
-        <v>56975</v>
+        <v>57664</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2320,21 +2320,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102961</v>
+        <v>103020</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2374,12 +2374,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124227864</v>
+        <v>124226880</v>
       </c>
       <c r="B17" t="n">
-        <v>56942</v>
+        <v>56975</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,33 +2418,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100091</v>
+        <v>102961</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>mjällbo, Vg</t>
@@ -2481,22 +2476,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:35</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:35</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,10 +2508,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124227773</v>
+        <v>124227864</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>56942</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,20 +2520,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100091</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2557,6 +2542,11 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>mjällbo, Vg</t>
@@ -2596,9 +2586,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>00:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2625,10 +2625,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124227087</v>
+        <v>124227160</v>
       </c>
       <c r="B19" t="n">
-        <v>57664</v>
+        <v>57532</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2637,25 +2637,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103020</v>
+        <v>102977</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124226790</v>
+        <v>124227197</v>
       </c>
       <c r="B20" t="n">
-        <v>57948</v>
+        <v>58191</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2739,31 +2739,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102999</v>
+        <v>103044</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>mjällbo, mjällbo, Vg</t>
+          <t>mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -2829,10 +2829,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124227197</v>
+        <v>124227773</v>
       </c>
       <c r="B21" t="n">
-        <v>58191</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2841,20 +2841,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124227160</v>
+        <v>124226790</v>
       </c>
       <c r="B22" t="n">
-        <v>57532</v>
+        <v>57948</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2943,20 +2943,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102977</v>
+        <v>102999</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2967,7 +2967,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>mjällbo, mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2304,10 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124227087</v>
+        <v>124227160</v>
       </c>
       <c r="B16" t="n">
-        <v>57664</v>
+        <v>57532</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2316,25 +2316,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103020</v>
+        <v>102977</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124226880</v>
+        <v>124227773</v>
       </c>
       <c r="B17" t="n">
-        <v>56975</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,21 +2422,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102961</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2476,12 +2476,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,10 +2508,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124227864</v>
+        <v>124226880</v>
       </c>
       <c r="B18" t="n">
-        <v>56942</v>
+        <v>56975</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2520,33 +2520,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100091</v>
+        <v>102961</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>mjällbo, Vg</t>
@@ -2583,22 +2578,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:35</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:35</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2625,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124227160</v>
+        <v>124227197</v>
       </c>
       <c r="B19" t="n">
-        <v>57532</v>
+        <v>58191</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2641,21 +2626,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102977</v>
+        <v>103044</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2727,10 +2712,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124227197</v>
+        <v>124227864</v>
       </c>
       <c r="B20" t="n">
-        <v>58191</v>
+        <v>56942</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2739,20 +2724,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103044</v>
+        <v>100091</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2761,6 +2746,11 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>mjällbo, Vg</t>
@@ -2800,9 +2790,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>00:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,10 +2829,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124227773</v>
+        <v>124227087</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>57664</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2845,16 +2845,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2304,10 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124227160</v>
+        <v>124227197</v>
       </c>
       <c r="B16" t="n">
-        <v>57532</v>
+        <v>58191</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2320,21 +2320,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102977</v>
+        <v>103044</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124227773</v>
+        <v>124227160</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>57532</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,25 +2418,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124226880</v>
+        <v>124227437</v>
       </c>
       <c r="B18" t="n">
-        <v>56975</v>
+        <v>57883</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2520,25 +2520,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102961</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124227197</v>
+        <v>124227864</v>
       </c>
       <c r="B19" t="n">
-        <v>58191</v>
+        <v>56942</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2622,20 +2622,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103044</v>
+        <v>100091</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2644,6 +2644,11 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>mjällbo, Vg</t>
@@ -2683,9 +2688,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>00:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2712,10 +2727,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124227864</v>
+        <v>124227773</v>
       </c>
       <c r="B20" t="n">
-        <v>56942</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,20 +2739,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100091</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2746,11 +2761,6 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>mjällbo, Vg</t>
@@ -2790,19 +2800,9 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:35</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124226790</v>
+        <v>124226880</v>
       </c>
       <c r="B22" t="n">
-        <v>57948</v>
+        <v>56975</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2947,16 +2947,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102999</v>
+        <v>102961</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2967,7 +2967,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>mjällbo, mjällbo, Vg</t>
+          <t>mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3033,10 +3033,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124227437</v>
+        <v>124226790</v>
       </c>
       <c r="B23" t="n">
-        <v>57883</v>
+        <v>57948</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3045,31 +3045,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>102999</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>mjällbo, mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2304,10 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124227197</v>
+        <v>124227864</v>
       </c>
       <c r="B16" t="n">
-        <v>58191</v>
+        <v>56942</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2316,20 +2316,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103044</v>
+        <v>100091</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2338,6 +2338,11 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>mjällbo, Vg</t>
@@ -2377,9 +2382,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>00:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,10 +2421,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124227160</v>
+        <v>124226790</v>
       </c>
       <c r="B17" t="n">
-        <v>57532</v>
+        <v>57948</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,20 +2433,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102977</v>
+        <v>102999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2442,7 +2457,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>mjällbo, mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2508,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124227437</v>
+        <v>124226880</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
+        <v>56975</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2520,25 +2535,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>102961</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2578,12 +2593,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,10 +2625,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124227864</v>
+        <v>124227087</v>
       </c>
       <c r="B19" t="n">
-        <v>56942</v>
+        <v>57664</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2622,20 +2637,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100091</v>
+        <v>103020</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2644,11 +2659,6 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>mjällbo, Vg</t>
@@ -2688,19 +2698,9 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:35</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2727,10 +2727,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124227773</v>
+        <v>124227160</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>57532</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2739,25 +2739,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124227087</v>
+        <v>124227773</v>
       </c>
       <c r="B21" t="n">
-        <v>57664</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2845,16 +2845,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124226880</v>
+        <v>124227437</v>
       </c>
       <c r="B22" t="n">
-        <v>56975</v>
+        <v>57883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2943,25 +2943,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102961</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3033,10 +3033,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124226790</v>
+        <v>124227197</v>
       </c>
       <c r="B23" t="n">
-        <v>57948</v>
+        <v>58191</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3045,31 +3045,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102999</v>
+        <v>103044</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>mjällbo, mjällbo, Vg</t>
+          <t>mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2931,10 +2931,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124227437</v>
+        <v>124227197</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>58191</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2947,16 +2947,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3033,10 +3033,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124227197</v>
+        <v>124227437</v>
       </c>
       <c r="B23" t="n">
-        <v>58191</v>
+        <v>57883</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3049,16 +3049,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2421,10 +2421,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124226790</v>
+        <v>124227087</v>
       </c>
       <c r="B17" t="n">
-        <v>57948</v>
+        <v>57664</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2437,27 +2437,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102999</v>
+        <v>103020</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>mjällbo, mjällbo, Vg</t>
+          <t>mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2523,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124226880</v>
+        <v>124227773</v>
       </c>
       <c r="B18" t="n">
-        <v>56975</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2539,21 +2539,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102961</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2625,10 +2625,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124227087</v>
+        <v>124226790</v>
       </c>
       <c r="B19" t="n">
-        <v>57664</v>
+        <v>57948</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2641,27 +2641,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103020</v>
+        <v>102999</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>mjällbo, mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -2829,10 +2829,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124227773</v>
+        <v>124227437</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2841,20 +2841,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3033,10 +3033,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124227437</v>
+        <v>124226880</v>
       </c>
       <c r="B23" t="n">
-        <v>57883</v>
+        <v>56975</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3045,25 +3045,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>102961</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3103,12 +3103,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2304,10 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124227864</v>
+        <v>124226790</v>
       </c>
       <c r="B16" t="n">
-        <v>56942</v>
+        <v>57948</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2316,36 +2316,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100091</v>
+        <v>102999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>mjällbo, mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -2382,19 +2377,9 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:35</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2421,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124227087</v>
+        <v>124226880</v>
       </c>
       <c r="B17" t="n">
-        <v>57664</v>
+        <v>56975</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2437,21 +2422,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103020</v>
+        <v>102961</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2491,12 +2476,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,10 +2508,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124227773</v>
+        <v>124227160</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>57532</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,25 +2520,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2625,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124226790</v>
+        <v>124227773</v>
       </c>
       <c r="B19" t="n">
-        <v>57948</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2641,27 +2626,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102999</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>mjällbo, mjällbo, Vg</t>
+          <t>mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -2727,10 +2712,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124227160</v>
+        <v>124227197</v>
       </c>
       <c r="B20" t="n">
-        <v>57532</v>
+        <v>58191</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2743,21 +2728,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102977</v>
+        <v>103044</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2829,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124227437</v>
+        <v>124227087</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>57664</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2841,20 +2826,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2931,10 +2916,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124227197</v>
+        <v>124227437</v>
       </c>
       <c r="B22" t="n">
-        <v>58191</v>
+        <v>57883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2947,16 +2932,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3033,10 +3018,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124226880</v>
+        <v>124227864</v>
       </c>
       <c r="B23" t="n">
-        <v>56975</v>
+        <v>56942</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3045,28 +3030,33 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102961</v>
+        <v>100091</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>mjällbo, Vg</t>
@@ -3103,12 +3093,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>00:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>00:35</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2304,10 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124226790</v>
+        <v>124227087</v>
       </c>
       <c r="B16" t="n">
-        <v>57948</v>
+        <v>57664</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2320,27 +2320,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102999</v>
+        <v>103020</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>mjällbo, mjällbo, Vg</t>
+          <t>mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -2406,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124226880</v>
+        <v>124226790</v>
       </c>
       <c r="B17" t="n">
-        <v>56975</v>
+        <v>57948</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,16 +2422,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102961</v>
+        <v>102999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2442,7 +2442,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>mjällbo, mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124227087</v>
+        <v>124227864</v>
       </c>
       <c r="B21" t="n">
-        <v>57664</v>
+        <v>56942</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2826,20 +2826,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103020</v>
+        <v>100091</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2848,6 +2848,11 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>mjällbo, Vg</t>
@@ -2887,9 +2892,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>00:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,10 +2931,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124227437</v>
+        <v>124226880</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>56975</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2928,25 +2943,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>102961</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2986,12 +3001,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3018,10 +3033,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124227864</v>
+        <v>124227437</v>
       </c>
       <c r="B23" t="n">
-        <v>56942</v>
+        <v>57883</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3030,20 +3045,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100091</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3052,11 +3067,6 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>mjällbo, Vg</t>
@@ -3096,19 +3106,9 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:35</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:35</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2304,10 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124227087</v>
+        <v>124227160</v>
       </c>
       <c r="B16" t="n">
-        <v>57664</v>
+        <v>57532</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2316,25 +2316,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103020</v>
+        <v>102977</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124227160</v>
+        <v>124227437</v>
       </c>
       <c r="B18" t="n">
-        <v>57532</v>
+        <v>57883</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,21 +2524,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102977</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124227864</v>
+        <v>124226880</v>
       </c>
       <c r="B21" t="n">
-        <v>56942</v>
+        <v>56975</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2826,33 +2826,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100091</v>
+        <v>102961</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>mjällbo, Vg</t>
@@ -2889,22 +2884,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:35</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:35</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2931,10 +2916,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124226880</v>
+        <v>124227087</v>
       </c>
       <c r="B22" t="n">
-        <v>56975</v>
+        <v>57664</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2947,21 +2932,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102961</v>
+        <v>103020</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3001,12 +2986,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3033,10 +3018,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124227437</v>
+        <v>124227864</v>
       </c>
       <c r="B23" t="n">
-        <v>57883</v>
+        <v>56942</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3045,20 +3030,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100091</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3067,6 +3052,11 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>mjällbo, Vg</t>
@@ -3106,9 +3096,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>00:35</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2304,10 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124227160</v>
+        <v>124227197</v>
       </c>
       <c r="B16" t="n">
-        <v>57532</v>
+        <v>58191</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2320,21 +2320,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102977</v>
+        <v>103044</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124226790</v>
+        <v>124227864</v>
       </c>
       <c r="B17" t="n">
-        <v>57948</v>
+        <v>56942</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,31 +2418,36 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102999</v>
+        <v>100091</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>mjällbo, mjällbo, Vg</t>
+          <t>mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2479,9 +2484,19 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>00:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2712,10 +2727,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124227197</v>
+        <v>124227160</v>
       </c>
       <c r="B20" t="n">
-        <v>58191</v>
+        <v>57532</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2728,21 +2743,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103044</v>
+        <v>102977</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2814,10 +2829,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124226880</v>
+        <v>124227087</v>
       </c>
       <c r="B21" t="n">
-        <v>56975</v>
+        <v>57664</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2830,21 +2845,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102961</v>
+        <v>103020</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2884,12 +2899,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,10 +2931,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124227087</v>
+        <v>124226880</v>
       </c>
       <c r="B22" t="n">
-        <v>57664</v>
+        <v>56975</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2932,21 +2947,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103020</v>
+        <v>102961</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2986,12 +3001,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3018,10 +3033,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124227864</v>
+        <v>124226790</v>
       </c>
       <c r="B23" t="n">
-        <v>56942</v>
+        <v>57948</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3030,36 +3045,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100091</v>
+        <v>102999</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>mjällbo, mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
@@ -3096,19 +3106,9 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:35</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:35</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2934,12 +2934,7 @@
         <v>124226880</v>
       </c>
       <c r="B22" t="n">
-        <v>56975</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57270</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2934,7 +2934,7 @@
         <v>124226880</v>
       </c>
       <c r="B22" t="n">
-        <v>57270</v>
+        <v>57278</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2934,7 +2934,7 @@
         <v>124226880</v>
       </c>
       <c r="B22" t="n">
-        <v>57278</v>
+        <v>57279</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -2934,7 +2934,7 @@
         <v>124226880</v>
       </c>
       <c r="B22" t="n">
-        <v>57279</v>
+        <v>57280</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,6 +3128,116 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131367148</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56769</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>på övervintringsplats</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>mjällbo, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>395619</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6370701</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -3133,7 +3133,7 @@
         <v>131367148</v>
       </c>
       <c r="B24" t="n">
-        <v>56769</v>
+        <v>56771</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -3133,7 +3133,7 @@
         <v>131367148</v>
       </c>
       <c r="B24" t="n">
-        <v>56771</v>
+        <v>56772</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -3133,7 +3133,7 @@
         <v>131367148</v>
       </c>
       <c r="B24" t="n">
-        <v>56777</v>
+        <v>56783</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -3133,7 +3133,7 @@
         <v>131367148</v>
       </c>
       <c r="B24" t="n">
-        <v>56783</v>
+        <v>56784</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -3133,7 +3133,7 @@
         <v>131367148</v>
       </c>
       <c r="B24" t="n">
-        <v>56784</v>
+        <v>56787</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -3133,7 +3133,7 @@
         <v>131367148</v>
       </c>
       <c r="B24" t="n">
-        <v>56787</v>
+        <v>56789</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -3243,7 +3243,7 @@
         <v>133663131</v>
       </c>
       <c r="B25" t="n">
-        <v>80494</v>
+        <v>80501</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>133695658</v>
       </c>
       <c r="B26" t="n">
-        <v>80330</v>
+        <v>80337</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>133662764</v>
       </c>
       <c r="B27" t="n">
-        <v>80330</v>
+        <v>80337</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>133772767</v>
       </c>
       <c r="B28" t="n">
-        <v>81055</v>
+        <v>81062</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>133772815</v>
       </c>
       <c r="B29" t="n">
-        <v>75326</v>
+        <v>75333</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>133772754</v>
       </c>
       <c r="B30" t="n">
-        <v>80389</v>
+        <v>80396</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5300359</v>
+        <v>107156314</v>
       </c>
       <c r="B2" t="n">
-        <v>107844</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222776</v>
+        <v>388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>395558.2612005109</v>
+        <v>395619</v>
       </c>
       <c r="R2" t="n">
-        <v>6370725.587045955</v>
+        <v>6370592</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-04-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-04-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,77 +759,68 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>hassellund</t>
+          <t>Mycket spännande trädklädd betesmark</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Lönn</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Henrik Weibull, Torbjørn Høitomt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2368331</v>
+        <v>133662764</v>
       </c>
       <c r="B3" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219955</v>
+        <v>388</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>Mjällbo, Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>395589.1133482009</v>
+        <v>395527</v>
       </c>
       <c r="R3" t="n">
-        <v>6370646.240105839</v>
+        <v>6370489</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,27 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>4 stänglar</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,84 +873,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>betesmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oscar Ljunggren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oscar Ljunggren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55482271</v>
+        <v>133695658</v>
       </c>
       <c r="B4" t="n">
-        <v>86132</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4374</v>
+        <v>388</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gul vaxskivling</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrocybe chlorophana</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Wünsche</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>Mjällbo, Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>395589.1133482009</v>
+        <v>395546</v>
       </c>
       <c r="R4" t="n">
-        <v>6370646.240105839</v>
+        <v>6370518</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-10-14</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-10-14</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,82 +978,82 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oscar Ljunggren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oscar Ljunggren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67711515</v>
+        <v>80829248</v>
       </c>
       <c r="B5" t="n">
-        <v>86134</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81025</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4377</v>
+        <v>738</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>395619.0861115475</v>
+        <v>395475</v>
       </c>
       <c r="R5" t="n">
-        <v>6370700.892286486</v>
+        <v>6370621</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,22 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-09-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-09-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,7 +1091,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1169,55 +1109,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>85847352</v>
+        <v>107156309</v>
       </c>
       <c r="B6" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81025</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219880</v>
+        <v>738</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mjällbo, Tranemo kommun, Götaland, Västra Götalands län, Vg</t>
+          <t>Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>395515.9218565605</v>
+        <v>395475</v>
       </c>
       <c r="R6" t="n">
-        <v>6370714.297191083</v>
+        <v>6370641</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,22 +1174,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:32</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:32</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,69 +1190,69 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Mycket spännande trädklädd betesmark</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Henrik Weibull, Torbjørn Høitomt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107156314</v>
+        <v>133772641</v>
       </c>
       <c r="B7" t="n">
-        <v>78472</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>388</v>
+        <v>738</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mjällbo, Vg</t>
+          <t>Mjällbo, Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>395618.4590016584</v>
+        <v>395480</v>
       </c>
       <c r="R7" t="n">
-        <v>6370592.219845636</v>
+        <v>6370600</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1353,22 +1276,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-10-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-10-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:47</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Har åtmintone spridit sig till stora spärrgrenade lönnen. Två mindre bålar på norrsidan</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,44 +1308,44 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Mycket spännande trädklädd betesmark</t>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Lönn</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Oscar Ljunggren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Henrik Weibull, Torbjørn Høitomt</t>
+          <t>Oscar Ljunggren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107156309</v>
+        <v>133772767</v>
       </c>
       <c r="B8" t="n">
-        <v>79136</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81069</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1441,17 +1369,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mjällbo, Vg</t>
+          <t>Mjällbo, Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>395475.2149100924</v>
+        <v>395487</v>
       </c>
       <c r="R8" t="n">
-        <v>6370640.550926764</v>
+        <v>6370649</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,22 +1403,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-10-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-10-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,36 +1429,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Mycket spännande trädklädd betesmark</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Oscar Ljunggren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Henrik Weibull, Torbjørn Høitomt</t>
+          <t>Oscar Ljunggren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107156308</v>
+        <v>80829244</v>
       </c>
       <c r="B9" t="n">
-        <v>78448</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,37 +1456,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003719</v>
+        <v>2667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>395475.2149100924</v>
+        <v>395475</v>
       </c>
       <c r="R9" t="n">
-        <v>6370640.550926764</v>
+        <v>6370621</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1592,22 +1512,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-23</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,82 +1526,68 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Mycket spännande trädklädd betesmark</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Henrik Weibull, Torbjørn Høitomt</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107156315</v>
+        <v>80829253</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>395618.4590016584</v>
+        <v>395475</v>
       </c>
       <c r="R10" t="n">
-        <v>6370592.219845636</v>
+        <v>6370621</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1715,22 +1611,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-10-23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-10-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,80 +1627,66 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Mycket spännande trädklädd betesmark</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Lönn</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Henrik Weibull, Torbjørn Høitomt</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110903723</v>
+        <v>80829250</v>
       </c>
       <c r="B11" t="n">
-        <v>100532</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223246</v>
+        <v>2779</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>395566.6317831297</v>
+        <v>395475</v>
       </c>
       <c r="R11" t="n">
-        <v>6370736.671594947</v>
+        <v>6370621</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1838,22 +1710,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,15 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110903247</v>
+        <v>55482271</v>
       </c>
       <c r="B12" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,38 +1753,47 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>4374</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hygrocybe chlorophana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.) Wünsche</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mjällbo, Tranemo kommun, Götaland, Västra Götalands län, Vg</t>
+          <t>mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>395515.9218565605</v>
+        <v>395589</v>
       </c>
       <c r="R12" t="n">
-        <v>6370714.297191083</v>
+        <v>6370646</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1951,22 +1817,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-05-07</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-05-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,6 +1831,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1993,15 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115162361</v>
+        <v>67711515</v>
       </c>
       <c r="B13" t="n">
-        <v>57315</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>89083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,37 +1861,47 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102621</v>
+        <v>4377</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Blodvaxing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mjällbo, Vg</t>
+          <t>mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>395508</v>
+        <v>395619</v>
       </c>
       <c r="R13" t="n">
-        <v>6370459</v>
+        <v>6370701</v>
       </c>
       <c r="S13" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2063,12 +1925,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2017-09-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2017-09-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,6 +1939,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2095,15 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115162360</v>
+        <v>133772815</v>
       </c>
       <c r="B14" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>75340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2111,37 +1969,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102622</v>
+        <v>6428</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mjällbo, Vg</t>
+          <t>Mjällbo, Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>395586</v>
+        <v>395505</v>
       </c>
       <c r="R14" t="n">
-        <v>6370534</v>
+        <v>6370709</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2165,12 +2023,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>07:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>07:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2181,74 +2049,79 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oscar Ljunggren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oscar Ljunggren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115369280</v>
+        <v>133662910</v>
       </c>
       <c r="B15" t="n">
-        <v>57371</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79753</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100048</v>
+        <v>6431</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mjällbo, Vg</t>
+          <t>Mjällbo, Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>395586</v>
+        <v>395528</v>
       </c>
       <c r="R15" t="n">
-        <v>6370534</v>
+        <v>6370527</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2272,12 +2145,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,27 +2175,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oscar Ljunggren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Oscar Ljunggren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124227197</v>
+        <v>80829245</v>
       </c>
       <c r="B16" t="n">
-        <v>58191</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2320,37 +2198,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103044</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Grönsiska</t>
-        </is>
+        <v>6455</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Scytinium lichenoides s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>395600</v>
+        <v>395475</v>
       </c>
       <c r="R16" t="n">
-        <v>6370617</v>
+        <v>6370621</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2374,12 +2244,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2019-11-10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2019-11-10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,58 +2276,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124227864</v>
+        <v>107156315</v>
       </c>
       <c r="B17" t="n">
-        <v>56942</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100091</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>395600</v>
+        <v>395619</v>
       </c>
       <c r="R17" t="n">
-        <v>6370617</v>
+        <v>6370592</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2481,22 +2346,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:35</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:35</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,69 +2362,74 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Mycket spännande trädklädd betesmark</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Lönn</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Henrik Weibull, Torbjørn Høitomt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124227437</v>
+        <v>107156326</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>395600</v>
+        <v>395564</v>
       </c>
       <c r="R18" t="n">
-        <v>6370617</v>
+        <v>6370561</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2593,12 +2453,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2021-10-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,69 +2469,70 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Mycket spännande trädklädd betesmark</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Thomas Tranefors</t>
+          <t>Henrik Weibull, Torbjørn Høitomt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124227773</v>
+        <v>80829148</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6471</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>395600</v>
+        <v>395429</v>
       </c>
       <c r="R19" t="n">
-        <v>6370617</v>
+        <v>6370571</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2695,12 +2556,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2019-11-10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2019-11-10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2727,53 +2588,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124227160</v>
+        <v>115369280</v>
       </c>
       <c r="B20" t="n">
-        <v>57532</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102977</v>
+        <v>100048</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>395600</v>
+        <v>395586</v>
       </c>
       <c r="R20" t="n">
-        <v>6370617</v>
+        <v>6370534</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2797,12 +2658,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,32 +2690,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124227087</v>
+        <v>124227773</v>
       </c>
       <c r="B21" t="n">
-        <v>57664</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2931,35 +2787,40 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124226880</v>
+        <v>124227864</v>
       </c>
       <c r="B22" t="n">
-        <v>57300</v>
+        <v>57340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102961</v>
+        <v>100091</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>mjällbo, Vg</t>
@@ -2996,12 +2857,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>00:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>00:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3028,15 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124226790</v>
+        <v>115162361</v>
       </c>
       <c r="B23" t="n">
-        <v>57948</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3044,37 +2910,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102999</v>
+        <v>102621</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>mjällbo, mjällbo, Vg</t>
+          <t>Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>395600</v>
+        <v>395508</v>
       </c>
       <c r="R23" t="n">
-        <v>6370617</v>
+        <v>6370459</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3098,12 +2964,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3130,27 +2996,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131367148</v>
+        <v>115162360</v>
       </c>
       <c r="B24" t="n">
-        <v>56789</v>
+        <v>57785</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>206002</v>
+        <v>102622</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3158,33 +3024,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>på övervintringsplats</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>mjällbo, Vg</t>
+          <t>Mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>395619</v>
+        <v>395586</v>
       </c>
       <c r="R24" t="n">
-        <v>6370701</v>
+        <v>6370534</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3208,12 +3061,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3240,10 +3093,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133663131</v>
+        <v>124226880</v>
       </c>
       <c r="B25" t="n">
-        <v>80501</v>
+        <v>57369</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,34 +3104,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229504</v>
+        <v>102961</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mjällbo, Mjällbo, Vg</t>
+          <t>mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>395527</v>
+        <v>395600</v>
       </c>
       <c r="R25" t="n">
-        <v>6370489</v>
+        <v>6370617</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3305,22 +3158,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>18:37</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>18:37</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,60 +3178,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Oscar Ljunggren</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Oscar Ljunggren</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133695658</v>
+        <v>124227160</v>
       </c>
       <c r="B26" t="n">
-        <v>80337</v>
+        <v>57947</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>388</v>
+        <v>102977</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mjällbo, Mjällbo, Vg</t>
+          <t>mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>395546</v>
+        <v>395600</v>
       </c>
       <c r="R26" t="n">
-        <v>6370518</v>
+        <v>6370617</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3412,22 +3255,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>20:18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>20:18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3438,41 +3271,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Oscar Ljunggren</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Oscar Ljunggren</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133662764</v>
+        <v>124226790</v>
       </c>
       <c r="B27" t="n">
-        <v>80337</v>
+        <v>58393</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,34 +3298,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>388</v>
+        <v>102999</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mjällbo, Mjällbo, Vg</t>
+          <t>mjällbo, mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>395527</v>
+        <v>395600</v>
       </c>
       <c r="R27" t="n">
-        <v>6370489</v>
+        <v>6370617</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3534,22 +3352,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>18:21</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>18:21</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,57 +3372,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Oscar Ljunggren</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Oscar Ljunggren</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133772767</v>
+        <v>124227437</v>
       </c>
       <c r="B28" t="n">
-        <v>81062</v>
+        <v>58327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>738</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mjällbo, Mjällbo, Vg</t>
+          <t>mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>395487</v>
+        <v>395600</v>
       </c>
       <c r="R28" t="n">
-        <v>6370649</v>
+        <v>6370617</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,22 +3449,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>06:56</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>06:56</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3671,57 +3469,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Oscar Ljunggren</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Oscar Ljunggren</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133772815</v>
+        <v>124227087</v>
       </c>
       <c r="B29" t="n">
-        <v>75333</v>
+        <v>58112</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6428</v>
+        <v>103020</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mjällbo, Mjällbo, Vg</t>
+          <t>mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>395505</v>
+        <v>395600</v>
       </c>
       <c r="R29" t="n">
-        <v>6370709</v>
+        <v>6370617</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,22 +3546,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>07:04</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>07:04</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3774,41 +3562,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Oscar Ljunggren</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Oscar Ljunggren</t>
+          <t>Thomas Tranefors</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133772754</v>
+        <v>124227197</v>
       </c>
       <c r="B30" t="n">
-        <v>80396</v>
+        <v>58636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3816,34 +3589,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6003719</v>
+        <v>103044</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mjällbo, Mjällbo, Vg</t>
+          <t>mjällbo, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>395475</v>
+        <v>395600</v>
       </c>
       <c r="R30" t="n">
-        <v>6370629</v>
+        <v>6370617</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3870,22 +3643,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>06:47</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>06:47</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3900,15 +3663,1264 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>110817408</v>
+      </c>
+      <c r="B31" t="n">
+        <v>45042</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>201164</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sexfläckig bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Zygaena filipendulae</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mjällbo, Vg</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>395511</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6370514</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-07-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-07-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131367148</v>
+      </c>
+      <c r="B32" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>på övervintringsplats</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>mjällbo, Vg</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>395619</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6370701</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>85847352</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mjällbo, Tranemo kommun, Götaland, Västra Götalands län, Vg</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>395516</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6370714</v>
+      </c>
+      <c r="S33" t="n">
+        <v>12</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2020-05-28</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2020-05-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2368331</v>
+      </c>
+      <c r="B34" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>mjällbo, Vg</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>395589</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6370646</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2011-05-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2011-05-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>4 stänglar</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>betesmark</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>80829149</v>
+      </c>
+      <c r="B35" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mjällbo, Vg</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>395429</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6370571</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2019-11-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2019-11-10</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>110903247</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mjällbo, Tranemo kommun, Götaland, Västra Götalands län, Vg</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>395516</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6370714</v>
+      </c>
+      <c r="S36" t="n">
+        <v>12</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-05-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-05-07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>5300359</v>
+      </c>
+      <c r="B37" t="n">
+        <v>111019</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222776</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Adoxa moschatellina</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>mjällbo, Vg</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>395558</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6370726</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2007-04-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2007-04-26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>hassellund</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>110903723</v>
+      </c>
+      <c r="B38" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>mjällbo, Vg</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>395567</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6370737</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>107156324</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mjällbo, Vg</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>395564</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6370561</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2021-10-23</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2021-10-23</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Mycket spännande trädklädd betesmark</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Henrik Weibull, Torbjørn Høitomt</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>133663131</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80508</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mjällbo, Mjällbo, Vg</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>395527</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6370489</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
           <t>Oscar Ljunggren</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>Oscar Ljunggren</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>107156308</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80357</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Mjällbo, Vg</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>395475</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6370641</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2021-10-23</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2021-10-23</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Mycket spännande trädklädd betesmark</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Henrik Weibull, Torbjørn Høitomt</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>133772754</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80403</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Mjällbo, Mjällbo, Vg</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>395475</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6370629</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>06:47</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>06:47</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Oscar Ljunggren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Oscar Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33970-2024 artfynd.xlsx
+++ b/artfynd/A 33970-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107156314</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133662764</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133695658</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80829248</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107156309</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1335,6 +1365,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133772641</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133772767</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1541,6 +1581,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80829244</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80829253</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1739,6 +1789,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80829250</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1847,6 +1902,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55482271</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1955,6 +2015,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67711515</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2077,6 +2142,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133772815</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2184,6 +2254,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133662910</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2273,6 +2348,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80829245</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2385,6 +2465,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107156315</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2487,6 +2572,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107156326</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2585,6 +2675,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80829148</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2687,6 +2782,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115369280</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2784,6 +2884,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124227773</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2896,6 +3001,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124227864</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2993,6 +3103,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115162361</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3090,6 +3205,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115162360</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3187,6 +3307,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124226880</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3284,6 +3409,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124227160</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3381,6 +3511,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124226790</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3478,6 +3613,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124227437</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3575,6 +3715,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124227087</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3672,6 +3817,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124227197</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3770,6 +3920,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110817408</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3880,6 +4035,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131367148</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3989,6 +4149,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85847352</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4105,6 +4270,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2368331</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4204,6 +4374,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80829149</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4302,6 +4477,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110903247</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4404,6 +4584,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5300359</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4502,6 +4687,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110903723</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4604,6 +4794,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107156324</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4711,6 +4906,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133663131</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4814,6 +5014,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107156308</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4921,8 +5126,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133772754</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>